--- a/courses_data/pg/degreeandprogram.xlsx
+++ b/courses_data/pg/degreeandprogram.xlsx
@@ -179,7 +179,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -201,12 +201,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -256,7 +250,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -278,12 +272,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="37.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
